--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA863A6A-5D1D-7748-B1C2-68D5FBD6DBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C530492-9310-214E-9322-1C0899868E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="8720" windowWidth="28760" windowHeight="16060" activeTab="1" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="8580" yWindow="8720" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -166,12 +166,6 @@
     <t>Foundation for Inference</t>
   </si>
   <si>
-    <t>Summarizing Data Part 1</t>
-  </si>
-  <si>
-    <t>Summarizing Data Part 2</t>
-  </si>
-  <si>
     <t>Maximum Likelihood Estimation</t>
   </si>
   <si>
@@ -217,19 +211,25 @@
     <t>NumDays</t>
   </si>
   <si>
-    <t>Presidents Day - No Meetup - Midterm</t>
-  </si>
-  <si>
     <t>Spring Break - No Meetup</t>
   </si>
   <si>
     <t>Linear Regression</t>
   </si>
   <si>
-    <t>Miedterm</t>
-  </si>
-  <si>
     <t>Intro to Course</t>
+  </si>
+  <si>
+    <t>Midterm</t>
+  </si>
+  <si>
+    <t>No Meetup - Midterm</t>
+  </si>
+  <si>
+    <t>Summarizing Data</t>
+  </si>
+  <si>
+    <t>TBD</t>
   </si>
 </sst>
 </file>
@@ -653,7 +653,7 @@
         <v>9</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G1" t="s">
         <v>41</v>
@@ -691,7 +691,7 @@
         <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H3" s="5"/>
     </row>
@@ -707,10 +707,10 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F4" s="8"/>
       <c r="H4" s="5"/>
@@ -727,10 +727,10 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H5" s="5"/>
     </row>
@@ -749,7 +749,7 @@
         <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F6" s="8"/>
       <c r="H6" s="4"/>
@@ -769,7 +769,7 @@
         <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -788,7 +788,7 @@
         <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H8" s="6"/>
     </row>
@@ -798,7 +798,7 @@
         <v>46097</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -817,7 +817,7 @@
         <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H10" s="4"/>
     </row>
@@ -836,7 +836,7 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H11" s="4"/>
     </row>
@@ -846,7 +846,7 @@
         <v>46118</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H12" s="6"/>
     </row>
@@ -862,10 +862,10 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H13" s="4"/>
     </row>
@@ -881,10 +881,10 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H14" s="8"/>
     </row>
@@ -903,7 +903,7 @@
         <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H15" s="4"/>
     </row>
@@ -922,7 +922,7 @@
         <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H16" s="6"/>
     </row>
@@ -974,7 +974,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>4</v>
@@ -998,7 +998,7 @@
         <v>46054</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1112,7 +1112,7 @@
         <v>46103</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
@@ -1185,7 +1185,7 @@
         <v>46138</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1201,7 +1201,7 @@
         <v>46145</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C530492-9310-214E-9322-1C0899868E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E58DEE-4647-F34A-917A-D1E5B921618D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="8720" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="1560" yWindow="11540" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -67,9 +67,6 @@
     <t>Link</t>
   </si>
   <si>
-    <t>/chapters/chapter1/</t>
-  </si>
-  <si>
     <t>Chatper 2 - Summarizing Data</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>Final Exam</t>
   </si>
   <si>
-    <t>/chatpers/chapter2/</t>
-  </si>
-  <si>
     <t>/chapters/chapter3</t>
   </si>
   <si>
@@ -157,9 +151,6 @@
     <t>Chapter 1 - Intro to Data, R, and RStudio</t>
   </si>
   <si>
-    <t>/assesssments/midterm/</t>
-  </si>
-  <si>
     <t>Slides</t>
   </si>
   <si>
@@ -230,6 +221,18 @@
   </si>
   <si>
     <t>TBD</t>
+  </si>
+  <si>
+    <t>/chatpers/chapter2</t>
+  </si>
+  <si>
+    <t>/chapters/chapter1</t>
+  </si>
+  <si>
+    <t>00-Intro_to_Course</t>
+  </si>
+  <si>
+    <t>LLcSKd7aSJU</t>
   </si>
 </sst>
 </file>
@@ -285,7 +288,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -308,6 +311,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -653,10 +657,10 @@
         <v>9</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H1" t="s">
         <v>2</v>
@@ -673,7 +677,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
       </c>
       <c r="H2" s="5"/>
     </row>
@@ -688,10 +698,10 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H3" s="5"/>
     </row>
@@ -707,10 +717,10 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F4" s="8"/>
       <c r="H4" s="5"/>
@@ -727,10 +737,10 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H5" s="5"/>
     </row>
@@ -746,10 +756,10 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F6" s="8"/>
       <c r="H6" s="4"/>
@@ -766,10 +776,10 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -785,10 +795,10 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H8" s="6"/>
     </row>
@@ -798,7 +808,7 @@
         <v>46097</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -814,10 +824,10 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H10" s="4"/>
     </row>
@@ -833,10 +843,10 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H11" s="4"/>
     </row>
@@ -846,7 +856,7 @@
         <v>46118</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H12" s="6"/>
     </row>
@@ -862,10 +872,10 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H13" s="4"/>
     </row>
@@ -881,10 +891,10 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H14" s="8"/>
     </row>
@@ -900,10 +910,10 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H15" s="4"/>
     </row>
@@ -919,10 +929,10 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H16" s="6"/>
     </row>
@@ -938,7 +948,7 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H17" s="4"/>
     </row>
@@ -974,7 +984,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>4</v>
@@ -998,10 +1008,7 @@
         <v>46054</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1017,10 +1024,10 @@
         <v>46068</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1036,10 +1043,10 @@
         <v>46075</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1055,10 +1062,10 @@
         <v>46082</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1074,10 +1081,10 @@
         <v>46089</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1093,10 +1100,10 @@
         <v>46096</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1112,10 +1119,7 @@
         <v>46103</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1131,10 +1135,10 @@
         <v>46117</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1150,10 +1154,10 @@
         <v>46124</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -1169,7 +1173,10 @@
         <v>46131</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1185,7 +1192,10 @@
         <v>46138</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1201,10 +1211,10 @@
         <v>46145</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1220,10 +1230,10 @@
         <v>46152</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1239,10 +1249,10 @@
         <v>46159</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E58DEE-4647-F34A-917A-D1E5B921618D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2E4BDD-9128-3C4A-A852-FCE2E6C16731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="11540" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="1480" yWindow="3580" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -232,7 +232,7 @@
     <t>00-Intro_to_Course</t>
   </si>
   <si>
-    <t>LLcSKd7aSJU</t>
+    <t>H2Lrb8nt3CU</t>
   </si>
 </sst>
 </file>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2E4BDD-9128-3C4A-A852-FCE2E6C16731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC32E5DE-98D7-AE43-80D2-E7103EE0ECD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="3580" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="1180" yWindow="10920" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
   <si>
     <t>Date</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>H2Lrb8nt3CU</t>
+  </si>
+  <si>
+    <t>01-Intro_to_Data</t>
+  </si>
+  <si>
+    <t>lSEuvYEj7wA</t>
   </si>
 </sst>
 </file>
@@ -703,6 +709,12 @@
       <c r="E3" t="s">
         <v>41</v>
       </c>
+      <c r="F3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" t="s">
+        <v>66</v>
+      </c>
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC32E5DE-98D7-AE43-80D2-E7103EE0ECD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C658A680-7FF4-8548-9955-FCF7C5AAFB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="10920" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -220,9 +220,6 @@
     <t>Summarizing Data</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>/chatpers/chapter2</t>
   </si>
   <si>
@@ -239,6 +236,31 @@
   </si>
   <si>
     <t>lSEuvYEj7wA</t>
+  </si>
+  <si>
+    <t>No Meetup</t>
+  </si>
+  <si>
+    <t>02-Summarizing_Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">letters
+vowels &lt;- c('a', 'e', 'i', 'o', 'u')
+letters %in% vowels
+letters %in% vowels |&gt; which()
+library(ggplot2)
+library(brickset)
+data(legosets)
+ggplot(legosets, aes(x = US_retailPrice)) + geom_histogram()
+ggplot(legosets, aes(x = US_retailPrice)) + geom_histogram(binwidth = 50)
+ggplot(legosets, aes(x = US_retailPrice)) + geom_histogram(bins = 40)
+ggplot(legosets, aes(x = US_retailPrice)) + geom_histogram()
+ggplot(legosets, aes(x = US_retailPrice, fill = availability)) + geom_histogram()
+ggplot(legosets, aes(x = US_retailPrice)) + geom_histogram(fill = 'white', color = 'purple')
+</t>
+  </si>
+  <si>
+    <t>58-rio8Micc</t>
   </si>
 </sst>
 </file>
@@ -686,10 +708,10 @@
         <v>34</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H2" s="5"/>
     </row>
@@ -710,14 +732,14 @@
         <v>41</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f>A3+7</f>
         <v>46062</v>
@@ -734,25 +756,23 @@
       <c r="E4" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="H4" s="5"/>
+      <c r="F4" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A17" si="0">A4+7</f>
         <v>46069</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="D5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="H5" s="5"/>
     </row>
@@ -1039,7 +1059,7 @@
         <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1058,7 +1078,7 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C658A680-7FF4-8548-9955-FCF7C5AAFB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F9CF79-79E7-4448-A843-733255516E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="10920" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t>Date</t>
   </si>
@@ -261,6 +261,12 @@
   </si>
   <si>
     <t>58-rio8Micc</t>
+  </si>
+  <si>
+    <t>N7Ol-6FKbGs</t>
+  </si>
+  <si>
+    <t>03-Probability</t>
   </si>
 </sst>
 </file>
@@ -793,7 +799,12 @@
       <c r="E6" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" t="s">
+        <v>72</v>
+      </c>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F9CF79-79E7-4448-A843-733255516E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0338D9-9310-D74E-B531-BE490E816C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="10920" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="75">
   <si>
     <t>Date</t>
   </si>
@@ -267,6 +267,12 @@
   </si>
   <si>
     <t>03-Probability</t>
+  </si>
+  <si>
+    <t>04-Distributions</t>
+  </si>
+  <si>
+    <t>UJBjoXSHZMY</t>
   </si>
 </sst>
 </file>
@@ -824,6 +830,12 @@
       <c r="E7" t="s">
         <v>44</v>
       </c>
+      <c r="F7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" t="s">
+        <v>73</v>
+      </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0338D9-9310-D74E-B531-BE490E816C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6D2A8D-61EB-554C-8B57-0ACD185F3C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="10920" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
   <si>
     <t>Date</t>
   </si>
@@ -273,6 +273,12 @@
   </si>
   <si>
     <t>UJBjoXSHZMY</t>
+  </si>
+  <si>
+    <t>05-Foundation_for_Inference</t>
+  </si>
+  <si>
+    <t>almTgoS2BGM</t>
   </si>
 </sst>
 </file>
@@ -855,6 +861,12 @@
       <c r="E8" t="s">
         <v>45</v>
       </c>
+      <c r="F8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" t="s">
+        <v>75</v>
+      </c>
       <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6D2A8D-61EB-554C-8B57-0ACD185F3C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB3E56B-D8DE-104A-96C6-0FF15AC28860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="10920" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="79">
   <si>
     <t>Date</t>
   </si>
@@ -279,6 +279,12 @@
   </si>
   <si>
     <t>almTgoS2BGM</t>
+  </si>
+  <si>
+    <t>06-Inference_for_Categorical_Data</t>
+  </si>
+  <si>
+    <t>SSxD2AFCCsY</t>
   </si>
 </sst>
 </file>
@@ -896,6 +902,12 @@
       <c r="E10" t="s">
         <v>46</v>
       </c>
+      <c r="F10" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" t="s">
+        <v>77</v>
+      </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB3E56B-D8DE-104A-96C6-0FF15AC28860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42F5F54-2017-D34A-89DB-AC8B86350E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="10920" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="81">
   <si>
     <t>Date</t>
   </si>
@@ -285,6 +285,12 @@
   </si>
   <si>
     <t>SSxD2AFCCsY</t>
+  </si>
+  <si>
+    <t>07-Inference_for_Numerical_Data</t>
+  </si>
+  <si>
+    <t>O-n-_pKTPLk</t>
   </si>
 </sst>
 </file>
@@ -927,6 +933,12 @@
       <c r="E11" t="s">
         <v>47</v>
       </c>
+      <c r="F11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42F5F54-2017-D34A-89DB-AC8B86350E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C530CC-0807-2441-B3C4-54AC8CF6E66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="10920" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="9700" yWindow="11280" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
   <si>
     <t>Date</t>
   </si>
@@ -291,6 +291,12 @@
   </si>
   <si>
     <t>O-n-_pKTPLk</t>
+  </si>
+  <si>
+    <t>08-Linear_Regression</t>
+  </si>
+  <si>
+    <t>mpQ740ctwtM</t>
   </si>
 </sst>
 </file>
@@ -968,6 +974,12 @@
       <c r="E13" t="s">
         <v>48</v>
       </c>
+      <c r="F13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" t="s">
+        <v>81</v>
+      </c>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C530CC-0807-2441-B3C4-54AC8CF6E66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0E3D8B-EA1D-FC4F-BD7C-D90ECD25482F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9700" yWindow="11280" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="620" yWindow="10940" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="85">
   <si>
     <t>Date</t>
   </si>
@@ -297,6 +297,12 @@
   </si>
   <si>
     <t>mpQ740ctwtM</t>
+  </si>
+  <si>
+    <t>09-Logistic_Regression</t>
+  </si>
+  <si>
+    <t>RPe8SjkKXdg</t>
   </si>
 </sst>
 </file>
@@ -999,6 +1005,12 @@
       <c r="E14" t="s">
         <v>49</v>
       </c>
+      <c r="F14" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" t="s">
+        <v>83</v>
+      </c>
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0E3D8B-EA1D-FC4F-BD7C-D90ECD25482F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667D6DB2-AADC-0E44-A91E-5FD8E21C593C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="620" yWindow="10940" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="87">
   <si>
     <t>Date</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>RPe8SjkKXdg</t>
+  </si>
+  <si>
+    <t>09-Multiple_Regression</t>
+  </si>
+  <si>
+    <t>A80rJ3QN1GM</t>
   </si>
 </sst>
 </file>
@@ -1030,6 +1036,12 @@
       <c r="E15" t="s">
         <v>49</v>
       </c>
+      <c r="F15" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" t="s">
+        <v>85</v>
+      </c>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667D6DB2-AADC-0E44-A91E-5FD8E21C593C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A629E226-001A-5748-8073-7FC0DB1AED3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="620" yWindow="10940" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -309,6 +309,12 @@
   </si>
   <si>
     <t>A80rJ3QN1GM</t>
+  </si>
+  <si>
+    <t>10-Bayesian_Analysis</t>
+  </si>
+  <si>
+    <t>hu-DMW9ZYpE</t>
   </si>
 </sst>
 </file>
@@ -1061,6 +1067,12 @@
       <c r="E16" t="s">
         <v>50</v>
       </c>
+      <c r="F16" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" t="s">
+        <v>87</v>
+      </c>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A629E226-001A-5748-8073-7FC0DB1AED3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B7A0C6-BED1-DD43-9198-D6FB4C309C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="620" yWindow="10940" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="91">
   <si>
     <t>Date</t>
   </si>
@@ -315,6 +315,12 @@
   </si>
   <si>
     <t>hu-DMW9ZYpE</t>
+  </si>
+  <si>
+    <t>11-Final_Meetup</t>
+  </si>
+  <si>
+    <t>ilO9Mzx1nUw</t>
   </si>
 </sst>
 </file>
@@ -1089,6 +1095,12 @@
       <c r="D17" t="s">
         <v>33</v>
       </c>
+      <c r="F17" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" t="s">
+        <v>89</v>
+      </c>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
